--- a/카드_아키타입/14_생활화학.xlsx
+++ b/카드_아키타입/14_생활화학.xlsx
@@ -381,7 +381,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="971550" cy="1047750"/>
+    <ext cx="962025" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2956,7 +2956,7 @@
       <row>121</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="111" name="Image 111" descr="Picture"/>
@@ -2981,7 +2981,7 @@
       <row>121</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="112" name="Image 112" descr="Picture"/>
@@ -3006,7 +3006,7 @@
       <row>121</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="113" name="Image 113" descr="Picture"/>
@@ -3031,7 +3031,7 @@
       <row>121</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="114" name="Image 114" descr="Picture"/>
@@ -3056,7 +3056,7 @@
       <row>121</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="115" name="Image 115" descr="Picture"/>
@@ -3081,7 +3081,7 @@
       <row>121</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="116" name="Image 116" descr="Picture"/>
@@ -4106,7 +4106,7 @@
       <row>182</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="157" name="Image 157" descr="Picture"/>
@@ -4131,7 +4131,7 @@
       <row>182</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="158" name="Image 158" descr="Picture"/>
@@ -4156,7 +4156,7 @@
       <row>182</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="159" name="Image 159" descr="Picture"/>
@@ -4181,7 +4181,7 @@
       <row>182</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="160" name="Image 160" descr="Picture"/>
@@ -4206,7 +4206,7 @@
       <row>182</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="161" name="Image 161" descr="Picture"/>
@@ -4231,7 +4231,7 @@
       <row>182</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="162" name="Image 162" descr="Picture"/>
@@ -4906,7 +4906,7 @@
       <row>206</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="189" name="Image 189" descr="Picture"/>
@@ -4931,7 +4931,7 @@
       <row>206</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="190" name="Image 190" descr="Picture"/>
@@ -4956,7 +4956,7 @@
       <row>206</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="191" name="Image 191" descr="Picture"/>

--- a/카드_아키타입/14_생활화학.xlsx
+++ b/카드_아키타입/14_생활화학.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="9029700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="9029700"/>
     <ext cx="1666875" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="9029700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="9029700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="10877550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>11</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="10877550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>11</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="10877550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>11</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="10877550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="12725400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="20091400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="20091400"/>
     <ext cx="1295400" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="20091400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="20091400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="21939250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="21939250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="21939250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="21939250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="23787100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="23787100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="32778700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="32778700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="32778700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="32778700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="34626550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="37338000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="37338000"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="37338000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="37338000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="39185850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="41109900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="41109900"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="41109900"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="41109900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="42957750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>52</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="42957750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>52</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="42957750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>52</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="42957750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="44805600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>52</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="44805600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>52</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="44805600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>52</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="44805600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="46653450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>52</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="46653450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>52</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="46653450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>52</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="46653450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="48501300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>52</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="48501300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>52</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="48501300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>52</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="48501300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>9239250</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="50349150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>52</row>
-      <rowOff>9239250</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="50349150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>52</row>
-      <rowOff>9239250</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="50349150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>52</row>
-      <rowOff>9239250</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="50349150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="58877200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="58877200"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="58877200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="58877200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="60725050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>65</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="60725050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>65</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="60725050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>65</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="60725050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="62572900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>65</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="62572900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>65</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="62572900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>65</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="62572900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="64420750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>65</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="64420750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>65</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="64420750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="67703700"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="67703700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="67703700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="67703700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="69551550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>76</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="69551550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>76</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="69551550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>76</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="69551550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="71399400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>76</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="71399400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>76</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="71399400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>76</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="71399400"/>
     <ext cx="1809750" cy="457200"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73247250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>76</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="73247250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>76</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="73247250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>76</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="73247250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="75095100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="81000600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="81000600"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="81000600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="81000600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="82848450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>88</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="82848450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>88</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="82848450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>88</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="82848450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="84696300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>88</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="84696300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>88</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="84696300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>88</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="84696300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="86544150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>88</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="86544150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>88</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="86544150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>88</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="86544150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="88392000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="91249500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="91249500"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="91249500"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="91249500"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="93097350"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>100</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="93097350"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>100</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="93097350"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>100</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="93097350"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="96824800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="96824800"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="96824800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="96824800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="98672650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>109</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="98672650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>109</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="98672650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>109</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="98672650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="100977700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="100977700"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="100977700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="100977700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="102825550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="102825550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="102825550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="102825550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="104673400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>118</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="104673400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>118</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="104673400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>118</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="104673400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="106521250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>118</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="106521250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>118</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="106521250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>118</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="106521250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="108369100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>130</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="111023400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>130</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="111023400"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>130</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="111023400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>130</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="111023400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>130</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="112871250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>141</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="116192300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>141</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="116192300"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>141</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="116192300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>141</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="116192300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>141</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="118040150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>141</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="118040150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>141</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="118040150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>141</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="118040150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="122174000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="122174000"/>
     <ext cx="1295400" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="122174000"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="122174000"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="124021850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="124021850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="124021850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="124021850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>161</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="125945900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>161</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="125945900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>161</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="125945900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>161</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="125945900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>161</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="127793750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>161</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="127793750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>161</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="127793750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>161</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="127793750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4448,14 +3598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>161</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="129641600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4473,14 +3618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>161</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="129641600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4498,14 +3638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>161</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="129641600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4523,14 +3658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>161</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="129641600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4548,14 +3678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>161</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="131489450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4573,14 +3698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>161</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="131489450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4598,14 +3718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>161</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="131489450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4623,14 +3738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>161</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="131489450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4648,14 +3758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>161</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="133337300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4673,14 +3778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>161</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="133337300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4698,14 +3798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>161</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="133337300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4723,14 +3818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>161</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="133337300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4748,14 +3838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>174</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="135261350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4773,14 +3858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>174</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="135261350"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4798,14 +3878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>174</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="135261350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4823,14 +3898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>174</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="135261350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4848,14 +3918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>174</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="137109200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4873,14 +3938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>174</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="137109200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4898,14 +3958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>174</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="137109200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4923,14 +3978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>174</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="137109200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4948,14 +3998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>174</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="138957050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4973,14 +4018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>174</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="138957050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4998,14 +4038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>174</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="138957050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5023,14 +4058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>184</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="140881100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5048,14 +4078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>184</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="140881100"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -5073,14 +4098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>184</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="140881100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5098,14 +4118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>184</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="140881100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5123,14 +4138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>184</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="142728950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5148,14 +4158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>184</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="142728950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5173,14 +4178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>184</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="142728950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5198,14 +4198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>184</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="142728950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5223,14 +4218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>194</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="150520400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5248,14 +4238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>194</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="150520400"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5273,14 +4258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>194</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="150520400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5298,14 +4278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>194</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="150520400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5323,14 +4298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>194</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="152368250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5348,14 +4318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>194</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="152368250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5373,14 +4338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>194</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="152368250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5398,14 +4358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>194</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="152368250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5423,14 +4378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>194</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="154216100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5448,14 +4398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>194</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="154216100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5473,14 +4418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>194</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="154216100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5498,14 +4438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>194</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="154216100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5523,14 +4458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>194</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="156063949"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5548,14 +4478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>204</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="157988000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5573,14 +4498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>204</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="157988000"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5598,14 +4518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>204</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="157988000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5623,14 +4538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>204</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="157988000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5648,14 +4558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>204</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="159835850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5673,14 +4578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>204</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="159835850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5698,14 +4598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>204</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="159835850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5723,14 +4618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>204</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="159835850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5748,14 +4638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>204</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="161683700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5773,14 +4658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>204</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="161683700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5798,14 +4678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>204</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="161683700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5823,14 +4698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>213</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="164782500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5848,14 +4718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>213</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="164782500"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5873,14 +4738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>213</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="164782500"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -5898,14 +4758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>213</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="164782500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5923,14 +4778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>213</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="166630350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5948,14 +4798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>213</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="166630350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5973,14 +4818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>213</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="166630350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5998,14 +4838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>213</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="166630350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6023,14 +4858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>213</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="168478200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6048,14 +4878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>224</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="170967400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6073,14 +4898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>224</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="170967400"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -6098,14 +4918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>224</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="170967400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6123,14 +4938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>224</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="170967400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6148,14 +4958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>224</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="172815250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6173,14 +4978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>233</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="174917100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6198,14 +4998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>233</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="174917100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6223,14 +5018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>233</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="174917100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6248,14 +5038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>233</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="174917100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6273,14 +5058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>233</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="176764950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6298,14 +5078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>233</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="176764950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6323,14 +5098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>233</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="176764950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6348,14 +5118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>233</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="176764950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6373,14 +5138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="179882800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6398,14 +5158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="179882800"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6423,14 +5178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="179882800"/>
     <ext cx="1809750" cy="676275"/>
     <pic>
       <nvPicPr>
@@ -6448,14 +5198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="179882800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6473,14 +5218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>242</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="181730650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6498,14 +5238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>242</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="181730650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6523,14 +5258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>242</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="181730650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6548,14 +5278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>242</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="181730650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6573,14 +5298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>242</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="183578500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6598,14 +5318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="186474100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6623,14 +5338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="186474100"/>
     <ext cx="1809750" cy="1524000"/>
     <pic>
       <nvPicPr>
@@ -6648,14 +5358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="186474100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6673,14 +5378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="186474100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6698,14 +5398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>253</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="188321950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6723,14 +5418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>253</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="188321950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6748,14 +5438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>253</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="188321950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6773,14 +5458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>253</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="188321950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6798,14 +5478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>262</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="192252600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6823,14 +5498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>262</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="192252600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6848,14 +5518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>262</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="192252600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6873,14 +5538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>262</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="192252600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6898,14 +5558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>262</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="194100450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6923,14 +5578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>275</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="197624700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6948,14 +5598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>275</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="197624700"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -6973,14 +5618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>275</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="197624700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6998,14 +5638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>275</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="197624700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7023,14 +5658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>275</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="199472550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7048,14 +5678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>275</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="199472550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7073,14 +5698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>275</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="199472550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7098,14 +5718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>275</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="199472550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7123,14 +5738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>284</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="204622400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7148,14 +5758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>284</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="204622400"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -7173,14 +5778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>284</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="204622400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7198,14 +5798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>284</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="204622400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7223,14 +5818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>284</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="206470250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7248,14 +5838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>284</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="206470250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7273,14 +5858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>284</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="206470250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7298,14 +5878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>284</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="206470250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7323,14 +5898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>293</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="209588100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7348,14 +5918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>293</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="209588100"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -7373,14 +5938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>293</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="209588100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7398,14 +5958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>293</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="209588100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7423,14 +5978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>293</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="211435950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7448,14 +5998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>293</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="211435950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7473,14 +6018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>293</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="211435950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7498,14 +6038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>293</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="211435950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7523,14 +6058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>302</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="214960200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7548,14 +6078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>302</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="214960200"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -7573,14 +6098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>302</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="214960200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7598,14 +6118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>302</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="214960200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7623,14 +6138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>302</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="216808050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7648,14 +6158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>302</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="216808050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7673,14 +6178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>302</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="216808050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7698,14 +6198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>302</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="216808050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7723,14 +6218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="220332300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7748,14 +6238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="220332300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7773,14 +6258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="220332300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7798,14 +6278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="220332300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7823,14 +6298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>327</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="229971600"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7848,14 +6318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>327</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="229971600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7873,14 +6338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>327</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="229971600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7898,14 +6358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>327</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="229971600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7923,14 +6378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>327</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="231819450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7948,14 +6398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>327</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="231819450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7973,14 +6418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>327</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="231819450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7998,14 +6438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="239204500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8023,14 +6458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="239204500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8048,14 +6478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="239204500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8073,14 +6498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="239204500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8098,14 +6518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>338</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="241052350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8123,14 +6538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>338</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="241052350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8148,14 +6558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>338</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="241052350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8173,14 +6578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="246811800"/>
     <ext cx="1809750" cy="1000125"/>
     <pic>
       <nvPicPr>
@@ -8198,14 +6598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="246811800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -8223,14 +6618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="246811800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -8248,14 +6638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="246811800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -8273,14 +6658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>360</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="252183900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8298,14 +6678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>360</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="252183900"/>
     <ext cx="1809750" cy="1285875"/>
     <pic>
       <nvPicPr>
@@ -8323,14 +6698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>360</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="252183900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8348,14 +6718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>360</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="252183900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8373,14 +6738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>360</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="254031750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8398,14 +6758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>360</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="254031750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8423,14 +6778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>360</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="254031750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8448,14 +6798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>360</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="254031750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8473,14 +6818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>370</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="259588000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8498,14 +6838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>370</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="259588000"/>
     <ext cx="1809750" cy="1019175"/>
     <pic>
       <nvPicPr>
@@ -8523,14 +6858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>370</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="259588000"/>
     <ext cx="1809750" cy="885825"/>
     <pic>
       <nvPicPr>
@@ -8548,14 +6878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>370</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="259588000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8573,14 +6898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>370</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="261435850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8598,14 +6918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>370</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="261435850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8623,14 +6938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>383</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="265366500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8648,14 +6958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>383</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="265366500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8673,14 +6978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>383</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="265366500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8698,14 +6998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>383</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="265366500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8723,14 +7018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>383</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="267214350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8748,14 +7038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>383</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="267214350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8773,14 +7058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>383</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="267214350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8798,14 +7078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>383</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="267214350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8823,14 +7098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>383</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="269062200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8848,14 +7118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>383</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="269062200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8873,14 +7138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>383</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="269062200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8898,14 +7158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>383</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="269062200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8923,14 +7178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>383</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="270910050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8948,14 +7198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>383</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="270910050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8973,14 +7218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>399</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="286791400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8998,14 +7238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>399</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="286791400"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -9023,14 +7258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>399</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="286791400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9048,14 +7278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>399</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="286791400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9073,14 +7298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>399</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="288639250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9098,14 +7318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>399</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="288639250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9123,14 +7338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>399</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="288639250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9148,14 +7358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>399</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="288639250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9173,14 +7378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>410</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="300088300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -9198,14 +7398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>410</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="300088300"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -9223,14 +7418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>410</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="300088300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9248,14 +7438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>410</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="300088300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9273,14 +7458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>410</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="301936150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9298,14 +7478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>410</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="301936150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9323,14 +7498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>410</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="301936150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9348,14 +7518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>410</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="301936150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9373,14 +7538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="310743600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -9398,14 +7558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="310743600"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9423,14 +7578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="310743600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9448,14 +7598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="310743600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9473,14 +7618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>421</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="312591450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9498,14 +7638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>421</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="312591450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9523,14 +7658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>421</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="312591450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9548,14 +7678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>421</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="312591450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9573,14 +7698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>430</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="318554100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9598,14 +7718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>430</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="318554100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9623,14 +7738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>430</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="318554100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9648,14 +7758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>430</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="318554100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9673,14 +7778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>430</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="320401950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9698,14 +7798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>430</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="320401950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9723,14 +7818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>430</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="320401950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9748,7 +7838,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/14_생활화학.xlsx
+++ b/카드_아키타입/14_생활화학.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="1847850"/>
+    <pos x="9239250" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="9029700"/>
+    <pos x="7391400" y="9029700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="9029700"/>
+    <pos x="9239250" y="9029700"/>
     <ext cx="1666875" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="9029700"/>
+    <pos x="11087100" y="9029700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="9029700"/>
+    <pos x="12934950" y="9029700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="10877550"/>
+    <pos x="7391400" y="10877550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="10877550"/>
+    <pos x="9239250" y="10877550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="10877550"/>
+    <pos x="11087100" y="10877550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="10877550"/>
+    <pos x="12934950" y="10877550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="12725400"/>
+    <pos x="7391400" y="12725400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="20091400"/>
+    <pos x="7391400" y="20091400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="20091400"/>
+    <pos x="9239250" y="20091400"/>
     <ext cx="1295400" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="20091400"/>
+    <pos x="11087100" y="20091400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="20091400"/>
+    <pos x="12934950" y="20091400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="21939250"/>
+    <pos x="7391400" y="21939250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="21939250"/>
+    <pos x="9239250" y="21939250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="21939250"/>
+    <pos x="11087100" y="21939250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="21939250"/>
+    <pos x="12934950" y="21939250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="23787100"/>
+    <pos x="7391400" y="23787100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="23787100"/>
+    <pos x="9239250" y="23787100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="32778700"/>
+    <pos x="7391400" y="32778700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="32778700"/>
+    <pos x="9239250" y="32778700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="32778700"/>
+    <pos x="11087100" y="32778700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="32778700"/>
+    <pos x="12934950" y="32778700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="34626550"/>
+    <pos x="7391400" y="34626550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="37338000"/>
+    <pos x="7391400" y="37338000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="37338000"/>
+    <pos x="9239250" y="37338000"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="37338000"/>
+    <pos x="11087100" y="37338000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="37338000"/>
+    <pos x="12934950" y="37338000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="39185850"/>
+    <pos x="7391400" y="39185850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="41109900"/>
+    <pos x="7391400" y="41109900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="41109900"/>
+    <pos x="9239250" y="41109900"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="41109900"/>
+    <pos x="11087100" y="41109900"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="41109900"/>
+    <pos x="12934950" y="41109900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="42957750"/>
+    <pos x="7391400" y="42957750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="42957750"/>
+    <pos x="9239250" y="42957750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="42957750"/>
+    <pos x="11087100" y="42957750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="42957750"/>
+    <pos x="12934950" y="42957750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="44805600"/>
+    <pos x="7391400" y="44805600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="44805600"/>
+    <pos x="9239250" y="44805600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="44805600"/>
+    <pos x="11087100" y="44805600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="44805600"/>
+    <pos x="12934950" y="44805600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="46653450"/>
+    <pos x="7391400" y="46653450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="46653450"/>
+    <pos x="9239250" y="46653450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="46653450"/>
+    <pos x="11087100" y="46653450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="46653450"/>
+    <pos x="12934950" y="46653450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="48501300"/>
+    <pos x="7391400" y="48501300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="48501300"/>
+    <pos x="9239250" y="48501300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="48501300"/>
+    <pos x="11087100" y="48501300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="48501300"/>
+    <pos x="12934950" y="48501300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="50349150"/>
+    <pos x="7391400" y="50349150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="50349150"/>
+    <pos x="9239250" y="50349150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="50349150"/>
+    <pos x="11087100" y="50349150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="50349150"/>
+    <pos x="12934950" y="50349150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="58877200"/>
+    <pos x="7391400" y="58877200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="58877200"/>
+    <pos x="9239250" y="58877200"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="58877200"/>
+    <pos x="11087100" y="58877200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="58877200"/>
+    <pos x="12934950" y="58877200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="60725050"/>
+    <pos x="7391400" y="60725050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="60725050"/>
+    <pos x="9239250" y="60725050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="60725050"/>
+    <pos x="11087100" y="60725050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="60725050"/>
+    <pos x="12934950" y="60725050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="62572900"/>
+    <pos x="7391400" y="62572900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="62572900"/>
+    <pos x="9239250" y="62572900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="62572900"/>
+    <pos x="11087100" y="62572900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="62572900"/>
+    <pos x="12934950" y="62572900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="64420750"/>
+    <pos x="7391400" y="64420750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="64420750"/>
+    <pos x="9239250" y="64420750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="64420750"/>
+    <pos x="11087100" y="64420750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="67703700"/>
+    <pos x="7391400" y="67703700"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="67703700"/>
+    <pos x="9239250" y="67703700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="67703700"/>
+    <pos x="11087100" y="67703700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="67703700"/>
+    <pos x="12934950" y="67703700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="69551550"/>
+    <pos x="7391400" y="69551550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="69551550"/>
+    <pos x="9239250" y="69551550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="69551550"/>
+    <pos x="11087100" y="69551550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="69551550"/>
+    <pos x="12934950" y="69551550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="71399400"/>
+    <pos x="7391400" y="71399400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="71399400"/>
+    <pos x="9239250" y="71399400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="71399400"/>
+    <pos x="11087100" y="71399400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="71399400"/>
+    <pos x="12934950" y="71399400"/>
     <ext cx="1809750" cy="457200"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73247250"/>
+    <pos x="7391400" y="73247250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="73247250"/>
+    <pos x="9239250" y="73247250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="73247250"/>
+    <pos x="11087100" y="73247250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="73247250"/>
+    <pos x="12934950" y="73247250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="75095100"/>
+    <pos x="7391400" y="75095100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="81000600"/>
+    <pos x="7391400" y="81000600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="81000600"/>
+    <pos x="9239250" y="81000600"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="81000600"/>
+    <pos x="11087100" y="81000600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="81000600"/>
+    <pos x="12934950" y="81000600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="82848450"/>
+    <pos x="7391400" y="82848450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="82848450"/>
+    <pos x="9239250" y="82848450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="82848450"/>
+    <pos x="11087100" y="82848450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="82848450"/>
+    <pos x="12934950" y="82848450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="84696300"/>
+    <pos x="7391400" y="84696300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="84696300"/>
+    <pos x="9239250" y="84696300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="84696300"/>
+    <pos x="11087100" y="84696300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="84696300"/>
+    <pos x="12934950" y="84696300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="86544150"/>
+    <pos x="7391400" y="86544150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="86544150"/>
+    <pos x="9239250" y="86544150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="86544150"/>
+    <pos x="11087100" y="86544150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="86544150"/>
+    <pos x="12934950" y="86544150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="88392000"/>
+    <pos x="7391400" y="88392000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="91249500"/>
+    <pos x="7391400" y="91249500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="91249500"/>
+    <pos x="9239250" y="91249500"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="91249500"/>
+    <pos x="11087100" y="91249500"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="91249500"/>
+    <pos x="12934950" y="91249500"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="93097350"/>
+    <pos x="7391400" y="93097350"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="93097350"/>
+    <pos x="9239250" y="93097350"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="93097350"/>
+    <pos x="11087100" y="93097350"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="93097350"/>
+    <pos x="12934950" y="93097350"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="96824800"/>
+    <pos x="7391400" y="96824800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="96824800"/>
+    <pos x="9239250" y="96824800"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="96824800"/>
+    <pos x="11087100" y="96824800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="96824800"/>
+    <pos x="12934950" y="96824800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="98672650"/>
+    <pos x="7391400" y="98672650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="98672650"/>
+    <pos x="9239250" y="98672650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="98672650"/>
+    <pos x="11087100" y="98672650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="98672650"/>
+    <pos x="12934950" y="98672650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="100977700"/>
+    <pos x="7391400" y="100977700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="100977700"/>
+    <pos x="9239250" y="100977700"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="100977700"/>
+    <pos x="11087100" y="100977700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="100977700"/>
+    <pos x="12934950" y="100977700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="102825550"/>
+    <pos x="7391400" y="102825550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="102825550"/>
+    <pos x="9239250" y="102825550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="102825550"/>
+    <pos x="11087100" y="102825550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="102825550"/>
+    <pos x="12934950" y="102825550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="104673400"/>
+    <pos x="7391400" y="104673400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="104673400"/>
+    <pos x="9239250" y="104673400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="104673400"/>
+    <pos x="11087100" y="104673400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="104673400"/>
+    <pos x="12934950" y="104673400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="106521250"/>
+    <pos x="7391400" y="106521250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="106521250"/>
+    <pos x="9239250" y="106521250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="106521250"/>
+    <pos x="11087100" y="106521250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="106521250"/>
+    <pos x="12934950" y="106521250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="108369100"/>
+    <pos x="7391400" y="108369100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="111023400"/>
+    <pos x="7391400" y="111023400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="111023400"/>
+    <pos x="9239250" y="111023400"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="111023400"/>
+    <pos x="11087100" y="111023400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="111023400"/>
+    <pos x="12934950" y="111023400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="112871250"/>
+    <pos x="7391400" y="112871250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="116192300"/>
+    <pos x="7391400" y="116192300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="116192300"/>
+    <pos x="9239250" y="116192300"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="116192300"/>
+    <pos x="11087100" y="116192300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="116192300"/>
+    <pos x="12934950" y="116192300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="118040150"/>
+    <pos x="7391400" y="118040150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="118040150"/>
+    <pos x="9239250" y="118040150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="118040150"/>
+    <pos x="11087100" y="118040150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="118040150"/>
+    <pos x="12934950" y="118040150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="122174000"/>
+    <pos x="7391400" y="122174000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="122174000"/>
+    <pos x="9239250" y="122174000"/>
     <ext cx="1295400" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="122174000"/>
+    <pos x="11087100" y="122174000"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="122174000"/>
+    <pos x="12934950" y="122174000"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="124021850"/>
+    <pos x="7391400" y="124021850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="124021850"/>
+    <pos x="9239250" y="124021850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="124021850"/>
+    <pos x="11087100" y="124021850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="124021850"/>
+    <pos x="12934950" y="124021850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="125945900"/>
+    <pos x="7391400" y="125945900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="125945900"/>
+    <pos x="9239250" y="125945900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="125945900"/>
+    <pos x="11087100" y="125945900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="125945900"/>
+    <pos x="12934950" y="125945900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="127793750"/>
+    <pos x="7391400" y="127793750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="127793750"/>
+    <pos x="9239250" y="127793750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="127793750"/>
+    <pos x="11087100" y="127793750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="127793750"/>
+    <pos x="12934950" y="127793750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="129641600"/>
+    <pos x="7391400" y="129641600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="129641600"/>
+    <pos x="9239250" y="129641600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="129641600"/>
+    <pos x="11087100" y="129641600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="129641600"/>
+    <pos x="12934950" y="129641600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="131489450"/>
+    <pos x="7391400" y="131489450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="131489450"/>
+    <pos x="9239250" y="131489450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="131489450"/>
+    <pos x="11087100" y="131489450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="131489450"/>
+    <pos x="12934950" y="131489450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="133337300"/>
+    <pos x="7391400" y="133337300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="133337300"/>
+    <pos x="9239250" y="133337300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="133337300"/>
+    <pos x="11087100" y="133337300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="133337300"/>
+    <pos x="12934950" y="133337300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="135261350"/>
+    <pos x="7391400" y="135261350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="135261350"/>
+    <pos x="9239250" y="135261350"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="135261350"/>
+    <pos x="11087100" y="135261350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="135261350"/>
+    <pos x="12934950" y="135261350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="137109200"/>
+    <pos x="7391400" y="137109200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="137109200"/>
+    <pos x="9239250" y="137109200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="137109200"/>
+    <pos x="11087100" y="137109200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="137109200"/>
+    <pos x="12934950" y="137109200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="138957050"/>
+    <pos x="7391400" y="138957050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="138957050"/>
+    <pos x="9239250" y="138957050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="138957050"/>
+    <pos x="11087100" y="138957050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="140881100"/>
+    <pos x="7391400" y="140881100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="140881100"/>
+    <pos x="9239250" y="140881100"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="140881100"/>
+    <pos x="11087100" y="140881100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="140881100"/>
+    <pos x="12934950" y="140881100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="142728950"/>
+    <pos x="7391400" y="142728950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="142728950"/>
+    <pos x="9239250" y="142728950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="142728950"/>
+    <pos x="11087100" y="142728950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="142728950"/>
+    <pos x="12934950" y="142728950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="150520400"/>
+    <pos x="7391400" y="150520400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="150520400"/>
+    <pos x="9239250" y="150520400"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="150520400"/>
+    <pos x="11087100" y="150520400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="150520400"/>
+    <pos x="12934950" y="150520400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="152368250"/>
+    <pos x="7391400" y="152368250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="152368250"/>
+    <pos x="9239250" y="152368250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="152368250"/>
+    <pos x="11087100" y="152368250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="152368250"/>
+    <pos x="12934950" y="152368250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="154216100"/>
+    <pos x="7391400" y="154216100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="154216100"/>
+    <pos x="9239250" y="154216100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="154216100"/>
+    <pos x="11087100" y="154216100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="154216100"/>
+    <pos x="12934950" y="154216100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="156063949"/>
+    <pos x="7391400" y="156063949"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="157988000"/>
+    <pos x="7391400" y="157988000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="157988000"/>
+    <pos x="9239250" y="157988000"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="157988000"/>
+    <pos x="11087100" y="157988000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="157988000"/>
+    <pos x="12934950" y="157988000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="159835850"/>
+    <pos x="7391400" y="159835850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="159835850"/>
+    <pos x="9239250" y="159835850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="159835850"/>
+    <pos x="11087100" y="159835850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="159835850"/>
+    <pos x="12934950" y="159835850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="161683700"/>
+    <pos x="7391400" y="161683700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="161683700"/>
+    <pos x="9239250" y="161683700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="161683700"/>
+    <pos x="11087100" y="161683700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="164782500"/>
+    <pos x="7391400" y="164782500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="164782500"/>
+    <pos x="9239250" y="164782500"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="164782500"/>
+    <pos x="11087100" y="164782500"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="164782500"/>
+    <pos x="12934950" y="164782500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="166630350"/>
+    <pos x="7391400" y="166630350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="166630350"/>
+    <pos x="9239250" y="166630350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="166630350"/>
+    <pos x="11087100" y="166630350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="166630350"/>
+    <pos x="12934950" y="166630350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="168478200"/>
+    <pos x="7391400" y="168478200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="170967400"/>
+    <pos x="7391400" y="170967400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="170967400"/>
+    <pos x="9239250" y="170967400"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="170967400"/>
+    <pos x="11087100" y="170967400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="170967400"/>
+    <pos x="12934950" y="170967400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="172815250"/>
+    <pos x="7391400" y="172815250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="174917100"/>
+    <pos x="7391400" y="174917100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="174917100"/>
+    <pos x="9239250" y="174917100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="174917100"/>
+    <pos x="11087100" y="174917100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="174917100"/>
+    <pos x="12934950" y="174917100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="176764950"/>
+    <pos x="7391400" y="176764950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="176764950"/>
+    <pos x="9239250" y="176764950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="176764950"/>
+    <pos x="11087100" y="176764950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="176764950"/>
+    <pos x="12934950" y="176764950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="179882800"/>
+    <pos x="7391400" y="179882800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="179882800"/>
+    <pos x="9239250" y="179882800"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="179882800"/>
+    <pos x="11087100" y="179882800"/>
     <ext cx="1809750" cy="676275"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="179882800"/>
+    <pos x="12934950" y="179882800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5220,7 +5220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="181730650"/>
+    <pos x="7391400" y="181730650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5240,7 +5240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="181730650"/>
+    <pos x="9239250" y="181730650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5260,7 +5260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="181730650"/>
+    <pos x="11087100" y="181730650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5280,7 +5280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="181730650"/>
+    <pos x="12934950" y="181730650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5300,7 +5300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="183578500"/>
+    <pos x="7391400" y="183578500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5320,7 +5320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="186474100"/>
+    <pos x="7391400" y="186474100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5340,7 +5340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="186474100"/>
+    <pos x="9239250" y="186474100"/>
     <ext cx="1809750" cy="1524000"/>
     <pic>
       <nvPicPr>
@@ -5360,7 +5360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="186474100"/>
+    <pos x="11087100" y="186474100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5380,7 +5380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="186474100"/>
+    <pos x="12934950" y="186474100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5400,7 +5400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="188321950"/>
+    <pos x="7391400" y="188321950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5420,7 +5420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="188321950"/>
+    <pos x="9239250" y="188321950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5440,7 +5440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="188321950"/>
+    <pos x="11087100" y="188321950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5460,7 +5460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="188321950"/>
+    <pos x="12934950" y="188321950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5480,7 +5480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="192252600"/>
+    <pos x="7391400" y="192252600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5500,7 +5500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="192252600"/>
+    <pos x="9239250" y="192252600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5520,7 +5520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="192252600"/>
+    <pos x="11087100" y="192252600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5540,7 +5540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="192252600"/>
+    <pos x="12934950" y="192252600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5560,7 +5560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="194100450"/>
+    <pos x="7391400" y="194100450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5580,7 +5580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="197624700"/>
+    <pos x="7391400" y="197624700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5600,7 +5600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="197624700"/>
+    <pos x="9239250" y="197624700"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -5620,7 +5620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="197624700"/>
+    <pos x="11087100" y="197624700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5640,7 +5640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="197624700"/>
+    <pos x="12934950" y="197624700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5660,7 +5660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="199472550"/>
+    <pos x="7391400" y="199472550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5680,7 +5680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="199472550"/>
+    <pos x="9239250" y="199472550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5700,7 +5700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="199472550"/>
+    <pos x="11087100" y="199472550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5720,7 +5720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="199472550"/>
+    <pos x="12934950" y="199472550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5740,7 +5740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="204622400"/>
+    <pos x="7391400" y="204622400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5760,7 +5760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="204622400"/>
+    <pos x="9239250" y="204622400"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -5780,7 +5780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="204622400"/>
+    <pos x="11087100" y="204622400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5800,7 +5800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="204622400"/>
+    <pos x="12934950" y="204622400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5820,7 +5820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="206470250"/>
+    <pos x="7391400" y="206470250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5840,7 +5840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="206470250"/>
+    <pos x="9239250" y="206470250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5860,7 +5860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="206470250"/>
+    <pos x="11087100" y="206470250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5880,7 +5880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="206470250"/>
+    <pos x="12934950" y="206470250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5900,7 +5900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="209588100"/>
+    <pos x="7391400" y="209588100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5920,7 +5920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="209588100"/>
+    <pos x="9239250" y="209588100"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -5940,7 +5940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="209588100"/>
+    <pos x="11087100" y="209588100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5960,7 +5960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="209588100"/>
+    <pos x="12934950" y="209588100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5980,7 +5980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="211435950"/>
+    <pos x="7391400" y="211435950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6000,7 +6000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="211435950"/>
+    <pos x="9239250" y="211435950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6020,7 +6020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="211435950"/>
+    <pos x="11087100" y="211435950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6040,7 +6040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="211435950"/>
+    <pos x="12934950" y="211435950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6060,7 +6060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="214960200"/>
+    <pos x="7391400" y="214960200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6080,7 +6080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="214960200"/>
+    <pos x="9239250" y="214960200"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -6100,7 +6100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="214960200"/>
+    <pos x="11087100" y="214960200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6120,7 +6120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="214960200"/>
+    <pos x="12934950" y="214960200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6140,7 +6140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="216808050"/>
+    <pos x="7391400" y="216808050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6160,7 +6160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="216808050"/>
+    <pos x="9239250" y="216808050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6180,7 +6180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="216808050"/>
+    <pos x="11087100" y="216808050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6200,7 +6200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="216808050"/>
+    <pos x="12934950" y="216808050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6220,7 +6220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="220332300"/>
+    <pos x="7391400" y="220332300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6240,7 +6240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="220332300"/>
+    <pos x="9239250" y="220332300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6260,7 +6260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="220332300"/>
+    <pos x="11087100" y="220332300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6280,7 +6280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="220332300"/>
+    <pos x="12934950" y="220332300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6300,7 +6300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="229971600"/>
+    <pos x="7391400" y="229971600"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6320,7 +6320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="229971600"/>
+    <pos x="9239250" y="229971600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6340,7 +6340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="229971600"/>
+    <pos x="11087100" y="229971600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6360,7 +6360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="229971600"/>
+    <pos x="12934950" y="229971600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6380,7 +6380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="231819450"/>
+    <pos x="7391400" y="231819450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6400,7 +6400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="231819450"/>
+    <pos x="9239250" y="231819450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6420,7 +6420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="231819450"/>
+    <pos x="11087100" y="231819450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6440,7 +6440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="239204500"/>
+    <pos x="7391400" y="239204500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6460,7 +6460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="239204500"/>
+    <pos x="9239250" y="239204500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6480,7 +6480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="239204500"/>
+    <pos x="11087100" y="239204500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6500,7 +6500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="239204500"/>
+    <pos x="12934950" y="239204500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6520,7 +6520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="241052350"/>
+    <pos x="7391400" y="241052350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6540,7 +6540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="241052350"/>
+    <pos x="9239250" y="241052350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6560,7 +6560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="241052350"/>
+    <pos x="11087100" y="241052350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6580,7 +6580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="246811800"/>
+    <pos x="7391400" y="246811800"/>
     <ext cx="1809750" cy="1000125"/>
     <pic>
       <nvPicPr>
@@ -6600,7 +6600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="246811800"/>
+    <pos x="9239250" y="246811800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6620,7 +6620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="246811800"/>
+    <pos x="11087100" y="246811800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6640,7 +6640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="246811800"/>
+    <pos x="12934950" y="246811800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6660,7 +6660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="252183900"/>
+    <pos x="7391400" y="252183900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6680,7 +6680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="252183900"/>
+    <pos x="9239250" y="252183900"/>
     <ext cx="1809750" cy="1285875"/>
     <pic>
       <nvPicPr>
@@ -6700,7 +6700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="252183900"/>
+    <pos x="11087100" y="252183900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6720,7 +6720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="252183900"/>
+    <pos x="12934950" y="252183900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6740,7 +6740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="254031750"/>
+    <pos x="7391400" y="254031750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6760,7 +6760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="254031750"/>
+    <pos x="9239250" y="254031750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6780,7 +6780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="254031750"/>
+    <pos x="11087100" y="254031750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6800,7 +6800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="254031750"/>
+    <pos x="12934950" y="254031750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6820,7 +6820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="259588000"/>
+    <pos x="7391400" y="259588000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6840,7 +6840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="259588000"/>
+    <pos x="9239250" y="259588000"/>
     <ext cx="1809750" cy="1019175"/>
     <pic>
       <nvPicPr>
@@ -6860,7 +6860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="259588000"/>
+    <pos x="11087100" y="259588000"/>
     <ext cx="1809750" cy="885825"/>
     <pic>
       <nvPicPr>
@@ -6880,7 +6880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="259588000"/>
+    <pos x="12934950" y="259588000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6900,7 +6900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="261435850"/>
+    <pos x="7391400" y="261435850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6920,7 +6920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="261435850"/>
+    <pos x="9239250" y="261435850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6940,7 +6940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="265366500"/>
+    <pos x="7391400" y="265366500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6960,7 +6960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="265366500"/>
+    <pos x="9239250" y="265366500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6980,7 +6980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="265366500"/>
+    <pos x="11087100" y="265366500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7000,7 +7000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="265366500"/>
+    <pos x="12934950" y="265366500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7020,7 +7020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="267214350"/>
+    <pos x="7391400" y="267214350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7040,7 +7040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="267214350"/>
+    <pos x="9239250" y="267214350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7060,7 +7060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="267214350"/>
+    <pos x="11087100" y="267214350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7080,7 +7080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="267214350"/>
+    <pos x="12934950" y="267214350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7100,7 +7100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="269062200"/>
+    <pos x="7391400" y="269062200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7120,7 +7120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="269062200"/>
+    <pos x="9239250" y="269062200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7140,7 +7140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="269062200"/>
+    <pos x="11087100" y="269062200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7160,7 +7160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="269062200"/>
+    <pos x="12934950" y="269062200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7180,7 +7180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="270910050"/>
+    <pos x="7391400" y="270910050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7200,7 +7200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="270910050"/>
+    <pos x="9239250" y="270910050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7220,7 +7220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="286791400"/>
+    <pos x="7391400" y="286791400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7240,7 +7240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="286791400"/>
+    <pos x="9239250" y="286791400"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -7260,7 +7260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="286791400"/>
+    <pos x="11087100" y="286791400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7280,7 +7280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="286791400"/>
+    <pos x="12934950" y="286791400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7300,7 +7300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="288639250"/>
+    <pos x="7391400" y="288639250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7320,7 +7320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="288639250"/>
+    <pos x="9239250" y="288639250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7340,7 +7340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="288639250"/>
+    <pos x="11087100" y="288639250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7360,7 +7360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="288639250"/>
+    <pos x="12934950" y="288639250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7380,7 +7380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="300088300"/>
+    <pos x="7391400" y="300088300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7400,7 +7400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="300088300"/>
+    <pos x="9239250" y="300088300"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -7420,7 +7420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="300088300"/>
+    <pos x="11087100" y="300088300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7440,7 +7440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="300088300"/>
+    <pos x="12934950" y="300088300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7460,7 +7460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="301936150"/>
+    <pos x="7391400" y="301936150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7480,7 +7480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="301936150"/>
+    <pos x="9239250" y="301936150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7500,7 +7500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="301936150"/>
+    <pos x="11087100" y="301936150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7520,7 +7520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="301936150"/>
+    <pos x="12934950" y="301936150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7540,7 +7540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="310743600"/>
+    <pos x="7391400" y="310743600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7560,7 +7560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="310743600"/>
+    <pos x="9239250" y="310743600"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7580,7 +7580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="310743600"/>
+    <pos x="11087100" y="310743600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7600,7 +7600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="310743600"/>
+    <pos x="12934950" y="310743600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7620,7 +7620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="312591450"/>
+    <pos x="7391400" y="312591450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7640,7 +7640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="312591450"/>
+    <pos x="9239250" y="312591450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7660,7 +7660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="312591450"/>
+    <pos x="11087100" y="312591450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7680,7 +7680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="312591450"/>
+    <pos x="12934950" y="312591450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7700,7 +7700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="318554100"/>
+    <pos x="7391400" y="318554100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7720,7 +7720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="318554100"/>
+    <pos x="9239250" y="318554100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7740,7 +7740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="318554100"/>
+    <pos x="11087100" y="318554100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7760,7 +7760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="318554100"/>
+    <pos x="12934950" y="318554100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7780,7 +7780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="320401950"/>
+    <pos x="7391400" y="320401950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7800,7 +7800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="320401950"/>
+    <pos x="9239250" y="320401950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7820,7 +7820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="320401950"/>
+    <pos x="11087100" y="320401950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8138,7 +8138,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/14_생활화학.xlsx
+++ b/카드_아키타입/14_생활화학.xlsx
@@ -8669,12 +8669,12 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>0.85 비중. / 알콜,정제수, DPG / 적절하게 배합된 것. / 에센셜오일 골고루 분산, / 확산에 도움</t>
+          <t>0.85 비중. · 알콜,정제수, DPG · 적절하게 배합된 것. · 에센셜오일 골고루 분산 · 확산에 도움</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>향의 진함, 오래감에 따른 에센셜오일 함량 선택 / 모기가 싫어하는 4가지 에센셜오일 복합블랜딩오일. 시트로넬라, 유칼립투스, 레몬글라스, 제라늄</t>
+          <t>향의 진함, 오래감에 따른 에센셜오일 함량 선택 · 모기가 싫어하는 4가지 에센셜오일 복합블랜딩오일. 시트로넬라, 유칼립투스, 레몬글라스, 제라늄</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>0.85 비중. / 알콜,정제수, DPG / 적절하게 배합된 것. / 에센셜오일 골고루 분산, / 확산에 도움</t>
+          <t>0.85 비중. · 알콜,정제수, DPG · 적절하게 배합된 것. · 에센셜오일 골고루 분산 · 확산에 도움</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>3~5% / ,장소, 환기여부에 따라 / 진한 향을 원하면 10%~25%까지 추가로 프러그런스를 더 넣어도 됩니다.</t>
+          <t>3~5% · 장소, 환기여부에 따라 · 진한 향을 원하면 10%~25%까지 추가로 프러그런스를 더 넣어도 됩니다.</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>3~5% / ,장소, 환기여부에 따라 / 진한 향을 원하면 10%~25%까지 추가로 프러그런스를 더 넣어도 됩니다.</t>
+          <t>3~5% · 장소, 환기여부에 따라 · 진한 향을 원하면 10%~25%까지 추가로 프러그런스를 더 넣어도 됩니다.</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
@@ -9121,10 +9121,10 @@
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>곡물 발효 알콜,</t>
-        </is>
-      </c>
-      <c r="F43" s="20" t="n"/>
+          <t>곡물 발효 알콜</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr"/>
     </row>
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
@@ -9322,10 +9322,10 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>곡물 발효 알콜,</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="n"/>
+          <t>곡물 발효 알콜</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>약 4%, 허브의 여왕, / 심신안정, 항균</t>
+          <t>약 4%, 허브의 여왕 · 심신안정, 항균</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>석고 대비 5%, 싱그러운 정원향, / 차량 실내 공간 크기나 향 강도에 대한 기호를 고려해 양조절 꼭하세요.</t>
+          <t>석고 대비 5%, 싱그러운 정원향 · 차량 실내 공간 크기나 향 강도에 대한 기호를 고려해 양조절 꼭하세요.</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>천연 에센셜오일 / (라벤더, 유칼리투스, 레몬, 페파민트 )</t>
+          <t>천연 에센셜오일 · (라벤더, 유칼리투스, 레몬, 페파민트 )</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>99%천연원석으로 만든 / 친환경 석고.</t>
+          <t>99%천연원석으로 만든 · 친환경 석고.</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>모기가 싫어하는 오일 집합! / 시트로넬라, 유칼립투스, 제라늄, 라벤더에센셜오일 복합 블랜딩오일.</t>
+          <t>모기가 싫어하는 오일 집합! · 시트로넬라, 유칼립투스, 제라늄, 라벤더에센셜오일 복합 블랜딩오일.</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>99%천연원석으로 만든 / 친환경 석고.</t>
+          <t>99%천연원석으로 만든 · 친환경 석고.</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>가용화제, / 물에 오일이 골고루 분산</t>
+          <t>가용화제 · 물에 오일이 골고루 분산</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>모기가 싫어하는 오일 집합! / 시트로넬라, 유칼립투스, 제라늄, 라벤더에센셜오일 / 복합 블랜딩오일.</t>
+          <t>모기가 싫어하는 오일 집합! · 시트로넬라, 유칼립투스, 제라늄, 라벤더에센셜오일 · 복합 블랜딩오일.</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="F93" s="20" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>99%천연원석으로 만든 / 친환경 석고.</t>
+          <t>99%천연원석으로 만든 · 친환경 석고.</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>가용화제, / 물에 오일이 골고루 분산</t>
+          <t>가용화제 · 물에 오일이 골고루 분산</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>프탈레이트 프리~. / 베이비 파우더향.</t>
+          <t>프탈레이트 프리~. · 베이비 파우더향.</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -10400,12 +10400,12 @@
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>99%천연원석으로 만든 / 친환경 석고.</t>
+          <t>99%천연원석으로 만든 · 친환경 석고.</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
@@ -10462,7 +10462,7 @@
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E108" s="10" t="n"/>
+      <c r="E108" s="10" t="inlineStr"/>
       <c r="F108" s="10" t="inlineStr">
         <is>
           <t>(원하는 색 아크릴, 포스터) 물감+물에 갠 것.</t>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="F117" s="20" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>사람피지성분과 비슷, / 사용감이 가벼운 오일</t>
+          <t>사람피지성분과 비슷 · 사용감이 가벼운 오일</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>원하는 에센셜오일 / 또는 프러스런스향 1g</t>
+          <t>원하는 에센셜오일 · 또는 프러스런스향 1g</t>
         </is>
       </c>
     </row>
@@ -10965,7 +10965,7 @@
       </c>
       <c r="E137" s="20" t="inlineStr">
         <is>
-          <t>가용화제, / 물에 오일이 골고루 분산</t>
+          <t>가용화제 · 물에 오일이 골고루 분산</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="F138" s="20" t="inlineStr">
         <is>
-          <t>천연 에센셜오일 / 또는 끌로에 우먼, 로즈듀에 등 / 프러그런스오일</t>
+          <t>천연 에센셜오일 · 또는 끌로에 우먼, 로즈듀에 등 · 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="E139" s="20" t="inlineStr">
         <is>
-          <t>순수한 물, / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>99%천연원석으로 만든 / 친환경 석고.</t>
+          <t>99%천연원석으로 만든 · 친환경 석고.</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E141" s="20" t="inlineStr">
         <is>
-          <t>0.85 비중. / 알콜,정제수, DPG / 적절하게 배합된 것. / 에센셜오일 골고루 분산, / 확산에 도움</t>
+          <t>0.85 비중. · 알콜,정제수, DPG · 적절하게 배합된 것. · 에센셜오일 골고루 분산 · 확산에 도움</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="E150" s="10" t="inlineStr">
         <is>
-          <t>가용화제, / 물에 오일이 골고루 분산</t>
+          <t>가용화제 · 물에 오일이 골고루 분산</t>
         </is>
       </c>
       <c r="F150" s="10" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>상록 침엽수로 / 스팀 증류법 추출, 숲향</t>
+          <t>상록 침엽수로 · 스팀 증류법 추출, 숲향</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
@@ -11324,7 +11324,7 @@
           <t>레몬글라스 잎을 비벼보면 레몬향이 남, 공기정화 , 벌레퇴치</t>
         </is>
       </c>
-      <c r="F152" s="10" t="n"/>
+      <c r="F152" s="10" t="inlineStr"/>
     </row>
     <row r="153" ht="112" customHeight="1">
       <c r="A153" s="10" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="F162" s="20" t="inlineStr">
         <is>
-          <t>히아신스 향 외 / 원하는 향</t>
+          <t>히아신스 향 외 · 원하는 향</t>
         </is>
       </c>
     </row>
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F163" s="20" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -11548,10 +11548,10 @@
       </c>
       <c r="E164" s="20" t="inlineStr">
         <is>
-          <t>방울수 추가 가능. / 식용색소로 처음에는 일부 뭉치지만 / 시간이 지나면 완전 녹습니다.</t>
-        </is>
-      </c>
-      <c r="F164" s="20" t="n"/>
+          <t>방울수 추가 가능. · 식용색소로 처음에는 일부 뭉치지만 · 시간이 지나면 완전 녹습니다.</t>
+        </is>
+      </c>
+      <c r="F164" s="20" t="inlineStr"/>
     </row>
     <row r="165" ht="14" customHeight="1">
       <c r="A165" s="15" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>히아신스, 로즈듀에 / 향 외 원하는 향</t>
+          <t>히아신스, 로즈듀에 · 향 외 원하는 향</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>75%. 디퓨저 전용 베이스. / 알코올보다 향을 오랫동안 지속.</t>
+          <t>75%. 디퓨저 전용 베이스. · 알코올보다 향을 오랫동안 지속.</t>
         </is>
       </c>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="E185" s="20" t="inlineStr">
         <is>
-          <t>모기가 싫어하는 허브에서 추출 100%천연오일. / 시트로넬라, 레몬글라스, 유칼립투스, / 제라늄 EO를 블랜딩한 것.</t>
+          <t>모기가 싫어하는 허브에서 추출 100%천연오일. · 시트로넬라, 레몬글라스, 유칼립투스 · 제라늄 EO를 블랜딩한 것.</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="E186" s="20" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12137,7 @@
           <t>베트남 공정무역 계피 칩,화학비료나 농약을 사용하지 않은 자연농법 재배.</t>
         </is>
       </c>
-      <c r="F197" s="10" t="n"/>
+      <c r="F197" s="10" t="inlineStr"/>
     </row>
     <row r="198" ht="32" customHeight="1">
       <c r="A198" s="10" t="inlineStr">
@@ -12165,7 +12165,7 @@
           <t>곡물 발효, 살균, 소독효과가 좋은 함량 70%</t>
         </is>
       </c>
-      <c r="F198" s="10" t="n"/>
+      <c r="F198" s="10" t="inlineStr"/>
     </row>
     <row r="199" ht="14" customHeight="1">
       <c r="A199" s="15" t="inlineStr">
@@ -12294,10 +12294,10 @@
       </c>
       <c r="E208" s="20" t="inlineStr">
         <is>
-          <t>염화칼슘과 숯이 / 더해져 제습, 탈취</t>
-        </is>
-      </c>
-      <c r="F208" s="20" t="n"/>
+          <t>염화칼슘과 숯이 · 더해져 제습, 탈취</t>
+        </is>
+      </c>
+      <c r="F208" s="20" t="inlineStr"/>
     </row>
     <row r="209" ht="16" customHeight="1">
       <c r="A209" s="20" t="inlineStr">
@@ -12325,7 +12325,7 @@
           <t>탈취 효과</t>
         </is>
       </c>
-      <c r="F209" s="20" t="n"/>
+      <c r="F209" s="20" t="inlineStr"/>
     </row>
     <row r="210" ht="32" customHeight="1">
       <c r="A210" s="20" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="F219" s="10" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="F230" s="20" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -12884,10 +12884,10 @@
       </c>
       <c r="E240" s="10" t="inlineStr">
         <is>
-          <t>100% 식품 첨가물, / 유럽산, 알카리</t>
-        </is>
-      </c>
-      <c r="F240" s="10" t="n"/>
+          <t>100% 식품 첨가물 · 유럽산, 알카리</t>
+        </is>
+      </c>
+      <c r="F240" s="10" t="inlineStr"/>
     </row>
     <row r="241" ht="16" customHeight="1">
       <c r="A241" s="10" t="inlineStr">
@@ -12912,10 +12912,10 @@
       </c>
       <c r="E241" s="10" t="inlineStr">
         <is>
-          <t>산소계 표백제, / 알카리</t>
-        </is>
-      </c>
-      <c r="F241" s="10" t="n"/>
+          <t>산소계 표백제 · 알카리</t>
+        </is>
+      </c>
+      <c r="F241" s="10" t="inlineStr"/>
     </row>
     <row r="242" ht="48" customHeight="1">
       <c r="A242" s="10" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E243" s="10" t="inlineStr">
         <is>
-          <t>복합유용미생물 / 발효액</t>
+          <t>복합유용미생물 · 발효액</t>
         </is>
       </c>
       <c r="F243" s="10" t="inlineStr">
@@ -13116,12 +13116,12 @@
       </c>
       <c r="E252" s="20" t="inlineStr">
         <is>
-          <t>향수, 룸스프레이 전용 베이스 / 분리현상이 없음. / (천연발효주정, 정제수, 유화제외)</t>
+          <t>향수, 룸스프레이 전용 베이스 · 분리현상이 없음. · (천연발효주정, 정제수, 유화제외)</t>
         </is>
       </c>
       <c r="F252" s="20" t="inlineStr">
         <is>
-          <t>아로마베이스70 / (분리될 수 있지만 숙성기간이 지나면 섞입니다. )</t>
+          <t>아로마베이스70 · (분리될 수 있지만 숙성기간이 지나면 섞입니다. )</t>
         </is>
       </c>
     </row>
@@ -13148,12 +13148,12 @@
       </c>
       <c r="E253" s="20" t="inlineStr">
         <is>
-          <t>천연 허브에서 추출한 정유. / 아로마테라피 효과</t>
+          <t>천연 허브에서 추출한 정유. · 아로마테라피 효과</t>
         </is>
       </c>
       <c r="F253" s="20" t="inlineStr">
         <is>
-          <t>아로마테라피효과 / 원하는 에센셜오일</t>
+          <t>아로마테라피효과 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -13292,12 +13292,12 @@
       </c>
       <c r="E262" s="10" t="inlineStr">
         <is>
-          <t>곡물 주정이 주원료. / 디퓨저 전용베이스</t>
+          <t>곡물 주정이 주원료. · 디퓨저 전용베이스</t>
         </is>
       </c>
       <c r="F262" s="10" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -13324,12 +13324,12 @@
       </c>
       <c r="E263" s="10" t="inlineStr">
         <is>
-          <t>25%, 프탈레이트 프리, / 원하는 향을 선택하세요.</t>
+          <t>25%, 프탈레이트 프리 · 원하는 향을 선택하세요.</t>
         </is>
       </c>
       <c r="F263" s="10" t="inlineStr">
         <is>
-          <t>히아신스, / 로즈듀에, / 레드로지스 등</t>
+          <t>히아신스 · 로즈듀에 · 레드로지스 등</t>
         </is>
       </c>
     </row>
@@ -13465,10 +13465,10 @@
       </c>
       <c r="E272" s="20" t="inlineStr">
         <is>
-          <t>애플계면활성제, / 라우릴글루코사이드, / 코코베타인, 글루카메이트, / 알로에베라잎즙, 편백수 등 에코인증, / 식물유래 순한 원료 함유.</t>
-        </is>
-      </c>
-      <c r="F272" s="20" t="n"/>
+          <t>애플계면활성제 · 라우릴글루코사이드 · 코코베타인, 글루카메이트 · 알로에베라잎즙, 편백수 등 에코인증 · 식물유래 순한 원료 함유.</t>
+        </is>
+      </c>
+      <c r="F272" s="20" t="inlineStr"/>
     </row>
     <row r="273" ht="64" customHeight="1">
       <c r="A273" s="20" t="inlineStr">
@@ -13528,7 +13528,7 @@
           <t>해조류, 풍부한 미네럴</t>
         </is>
       </c>
-      <c r="F274" s="20" t="n"/>
+      <c r="F274" s="20" t="inlineStr"/>
     </row>
     <row r="275" ht="32" customHeight="1">
       <c r="A275" s="20" t="inlineStr">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="E275" s="20" t="inlineStr">
         <is>
-          <t>합성향, 프탈레이트 프리. / 히아신스향</t>
+          <t>합성향, 프탈레이트 프리. · 히아신스향</t>
         </is>
       </c>
       <c r="F275" s="20" t="inlineStr">
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E284" s="10" t="inlineStr">
         <is>
-          <t>에코인증, / 콩왁스로 만든 왁스</t>
+          <t>에코인증 · 콩왁스로 만든 왁스</t>
         </is>
       </c>
       <c r="F284" s="10" t="inlineStr">
         <is>
-          <t>골든왁스, / 네이쳐왁스</t>
+          <t>골든왁스 · 네이쳐왁스</t>
         </is>
       </c>
     </row>
@@ -13738,12 +13738,12 @@
       </c>
       <c r="E285" s="10" t="inlineStr">
         <is>
-          <t>벌레가 싫어하는 시트로넬라, / 레몬그라스, 유칼립투스, / 제라늄EO를 블랜딩된것</t>
+          <t>벌레가 싫어하는 시트로넬라 · 레몬그라스, 유칼립투스 · 제라늄EO를 블랜딩된것</t>
         </is>
       </c>
       <c r="F285" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -13917,7 +13917,7 @@
           <t>사탕수수에서 채취한 점증제</t>
         </is>
       </c>
-      <c r="F295" s="20" t="n"/>
+      <c r="F295" s="20" t="inlineStr"/>
     </row>
     <row r="296" ht="32" customHeight="1">
       <c r="A296" s="20" t="inlineStr">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="E296" s="20" t="inlineStr">
         <is>
-          <t>사과에서 뽑아낸 / 음이온 계면활성제, / 생분해, 저자극</t>
+          <t>사과에서 뽑아낸 · 음이온 계면활성제 · 생분해, 저자극</t>
         </is>
       </c>
       <c r="F296" s="20" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="E297" s="20" t="inlineStr">
         <is>
-          <t>COCO-BETAIN, / 양쪽성, 저자극 세정제</t>
+          <t>COCO-BETAIN · 양쪽성, 저자극 세정제</t>
         </is>
       </c>
       <c r="F297" s="20" t="inlineStr">
         <is>
-          <t>애플 / 계면활성제</t>
+          <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="E298" s="20" t="inlineStr">
         <is>
-          <t>복합미생물발효액, / 곰팡이, 오염, 탈취 등</t>
+          <t>복합미생물발효액 · 곰팡이, 오염, 탈취 등</t>
         </is>
       </c>
       <c r="F298" s="20" t="inlineStr">
@@ -14038,12 +14038,12 @@
       </c>
       <c r="E299" s="20" t="inlineStr">
         <is>
-          <t>레몬껍질에서 추출, / 살균</t>
+          <t>레몬껍질에서 추출 · 살균</t>
         </is>
       </c>
       <c r="F299" s="20" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
           <t>천연 소재의 다공성 스톤</t>
         </is>
       </c>
-      <c r="F308" s="10" t="n"/>
+      <c r="F308" s="10" t="inlineStr"/>
     </row>
     <row r="309" ht="64" customHeight="1">
       <c r="A309" s="10" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="E309" s="10" t="inlineStr">
         <is>
-          <t>벌레가 싫어하는 / 시트로넬라, 유칼립투스, 제라늄, / 레몬그라스EO를 블랜딩한 오일 / 벌레기피제, 방향제 등으로 사용</t>
+          <t>벌레가 싫어하는 · 시트로넬라, 유칼립투스, 제라늄 · 레몬그라스EO를 블랜딩한 오일 · 벌레기피제, 방향제 등으로 사용</t>
         </is>
       </c>
       <c r="F309" s="10" t="inlineStr">
@@ -14365,7 +14365,7 @@
           <t>천연 소재의 다공성 스톤</t>
         </is>
       </c>
-      <c r="F318" s="20" t="n"/>
+      <c r="F318" s="20" t="inlineStr"/>
     </row>
     <row r="319" ht="32" customHeight="1">
       <c r="A319" s="20" t="inlineStr">
@@ -14390,12 +14390,12 @@
       </c>
       <c r="E319" s="20" t="inlineStr">
         <is>
-          <t>레몬, 레몬글라스, / 로즈우드EO 3가지 복합오일</t>
+          <t>레몬, 레몬글라스 · 로즈우드EO 3가지 복합오일</t>
         </is>
       </c>
       <c r="F319" s="20" t="inlineStr">
         <is>
-          <t>라임캔디 / 블랜딩오일</t>
+          <t>라임캔디 · 블랜딩오일</t>
         </is>
       </c>
     </row>
@@ -14545,7 +14545,7 @@
           <t>천연 소재의 다공성 스톤</t>
         </is>
       </c>
-      <c r="F328" s="10" t="n"/>
+      <c r="F328" s="10" t="inlineStr"/>
     </row>
     <row r="329" ht="32" customHeight="1">
       <c r="A329" s="10" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="E329" s="10" t="inlineStr">
         <is>
-          <t>레몬, 레몬글라스, 로즈우드 등 / 복합에센셜오일</t>
+          <t>레몬, 레몬글라스, 로즈우드 등 · 복합에센셜오일</t>
         </is>
       </c>
       <c r="F329" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -14717,7 +14717,7 @@
           <t>천연 소재의 다공성 스톤</t>
         </is>
       </c>
-      <c r="F338" s="20" t="n"/>
+      <c r="F338" s="20" t="inlineStr"/>
     </row>
     <row r="339" ht="32" customHeight="1">
       <c r="A339" s="20" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="F339" s="20" t="inlineStr">
         <is>
-          <t>스윗오렌지, / 네롤리EO 등</t>
+          <t>스윗오렌지 · 네롤리EO 등</t>
         </is>
       </c>
     </row>
@@ -14931,7 +14931,7 @@
           <t>사탕수수 유래점증제</t>
         </is>
       </c>
-      <c r="F349" s="10" t="n"/>
+      <c r="F349" s="10" t="inlineStr"/>
     </row>
     <row r="350" ht="16" customHeight="1">
       <c r="A350" s="10" t="inlineStr">
@@ -14988,10 +14988,10 @@
       </c>
       <c r="E351" s="10" t="inlineStr">
         <is>
-          <t>에코인증, 비이온 계면활성제,, / 코코넛알코올과 글루코스 (설탕, 전분)의 축합반응물</t>
-        </is>
-      </c>
-      <c r="F351" s="10" t="n"/>
+          <t>에코인증, 비이온 계면활성제 · 코코넛알코올과 글루코스 (설탕, 전분)의 축합반응물</t>
+        </is>
+      </c>
+      <c r="F351" s="10" t="inlineStr"/>
     </row>
     <row r="352" ht="48" customHeight="1">
       <c r="A352" s="10" t="inlineStr">
@@ -15048,10 +15048,10 @@
       </c>
       <c r="E353" s="10" t="inlineStr">
         <is>
-          <t>에코인증, / 코코넛오일이나 옥수수 감자 전분등에서 유래되는 비이온성 계면활성제</t>
-        </is>
-      </c>
-      <c r="F353" s="10" t="n"/>
+          <t>에코인증 · 코코넛오일이나 옥수수 감자 전분등에서 유래되는 비이온성 계면활성제</t>
+        </is>
+      </c>
+      <c r="F353" s="10" t="inlineStr"/>
     </row>
     <row r="354" ht="64" customHeight="1">
       <c r="A354" s="10" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="F354" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="F355" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="E356" s="10" t="inlineStr">
         <is>
-          <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
+          <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
       <c r="F356" s="10" t="inlineStr">
@@ -15289,10 +15289,10 @@
       </c>
       <c r="E365" s="20" t="inlineStr">
         <is>
-          <t>식물성 알코올, 살균, 소독,</t>
-        </is>
-      </c>
-      <c r="F365" s="20" t="n"/>
+          <t>식물성 알코올, 살균, 소독</t>
+        </is>
+      </c>
+      <c r="F365" s="20" t="inlineStr"/>
     </row>
     <row r="366" ht="48" customHeight="1">
       <c r="A366" s="20" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="E367" s="20" t="inlineStr">
         <is>
-          <t>합성향, 2ml 추천, / 기호에 맞게 농도, 향의 종류 / 조절 가능</t>
+          <t>합성향, 2ml 추천 · 기호에 맞게 농도, 향의 종류 · 조절 가능</t>
         </is>
       </c>
       <c r="F367" s="20" t="inlineStr">
@@ -15531,7 +15531,7 @@
           <t>탄탄한 유화 안정성, 부드러운 질감, 뛰어난 흡수력</t>
         </is>
       </c>
-      <c r="F377" s="10" t="n"/>
+      <c r="F377" s="10" t="inlineStr"/>
     </row>
     <row r="378" ht="48" customHeight="1">
       <c r="A378" s="10" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="F378" s="10" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="F379" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -15865,7 +15865,7 @@
       </c>
       <c r="E392" s="20" t="inlineStr">
         <is>
-          <t>복합한방추출물, / 균번식억제</t>
+          <t>복합한방추출물 · 균번식억제</t>
         </is>
       </c>
       <c r="F392" s="20" t="inlineStr">
@@ -16016,10 +16016,10 @@
       </c>
       <c r="E401" s="10" t="inlineStr">
         <is>
-          <t>'허브의 여왕' 라벤더는 긴장완화, 편안한 휴식, / 숙면, 살균, 진정,방충</t>
-        </is>
-      </c>
-      <c r="F401" s="10" t="n"/>
+          <t>'허브의 여왕' 라벤더는 긴장완화, 편안한 휴식 · 숙면, 살균, 진정,방충</t>
+        </is>
+      </c>
+      <c r="F401" s="10" t="inlineStr"/>
     </row>
     <row r="402" ht="64" customHeight="1">
       <c r="A402" s="10" t="inlineStr">
@@ -16047,7 +16047,7 @@
           <t>'땅의 사과'라는 그리스어에서 유래, 달콤함과 다양한 약리효과가 있는 캐모마일은 숙면, 정서적 진정, 영유아</t>
         </is>
       </c>
-      <c r="F402" s="10" t="n"/>
+      <c r="F402" s="10" t="inlineStr"/>
     </row>
     <row r="403" ht="16" customHeight="1">
       <c r="A403" s="10" t="inlineStr">
@@ -16075,7 +16075,7 @@
           <t>진정</t>
         </is>
       </c>
-      <c r="F403" s="10" t="n"/>
+      <c r="F403" s="10" t="inlineStr"/>
     </row>
     <row r="404" ht="14" customHeight="1">
       <c r="A404" s="15" t="inlineStr">
@@ -16215,10 +16215,10 @@
       </c>
       <c r="E412" s="20" t="inlineStr">
         <is>
-          <t>순수 아크릴 폴리머계열로서 / 흡수성 고분자, 물과 향을 흡수한 후 천천히 휘발시킴</t>
-        </is>
-      </c>
-      <c r="F412" s="20" t="n"/>
+          <t>순수 아크릴 폴리머계열로서 · 흡수성 고분자, 물과 향을 흡수한 후 천천히 휘발시킴</t>
+        </is>
+      </c>
+      <c r="F412" s="20" t="inlineStr"/>
     </row>
     <row r="413" ht="64" customHeight="1">
       <c r="A413" s="20" t="inlineStr">
@@ -16243,10 +16243,10 @@
       </c>
       <c r="E413" s="20" t="inlineStr">
         <is>
-          <t>뜨거운 물이나 따뜻한 물로 진행하면 1시간이내 불어납니다. / 차가운 물을 넣으시면 5~6시간 소요.</t>
-        </is>
-      </c>
-      <c r="F413" s="20" t="n"/>
+          <t>뜨거운 물이나 따뜻한 물로 진행하면 1시간이내 불어납니다. · 차가운 물을 넣으시면 5~6시간 소요.</t>
+        </is>
+      </c>
+      <c r="F413" s="20" t="inlineStr"/>
     </row>
     <row r="414" ht="16" customHeight="1">
       <c r="A414" s="20" t="inlineStr">
@@ -16306,7 +16306,7 @@
           <t>색내기용 첨가물</t>
         </is>
       </c>
-      <c r="F415" s="20" t="n"/>
+      <c r="F415" s="20" t="inlineStr"/>
     </row>
     <row r="416" ht="48" customHeight="1">
       <c r="A416" s="20" t="inlineStr">
@@ -16331,12 +16331,12 @@
       </c>
       <c r="E416" s="20" t="inlineStr">
         <is>
-          <t>레몬EO, 페파민트EO, 로즈마리EO, 일랑일랑EO 등 / 원하는 EO</t>
+          <t>레몬EO, 페파민트EO, 로즈마리EO, 일랑일랑EO 등 · 원하는 EO</t>
         </is>
       </c>
       <c r="F416" s="20" t="inlineStr">
         <is>
-          <t>아로마테라피효과 / 원하는 에센셜오일</t>
+          <t>아로마테라피효과 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="E417" s="20" t="inlineStr">
         <is>
-          <t>사과FO, 라일락FO, 복숭아FO, 자스민FO 등 / 원하는 프러스런스오일</t>
+          <t>사과FO, 라일락FO, 복숭아FO, 자스민FO 등 · 원하는 프러스런스오일</t>
         </is>
       </c>
       <c r="F417" s="20" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="E426" s="10" t="inlineStr">
         <is>
-          <t>에코인증, 콩기름으로 만든 양초베이스, 오래타고 인체무해, / 공기질향상</t>
+          <t>에코인증, 콩기름으로 만든 양초베이스, 오래타고 인체무해 · 공기질향상</t>
         </is>
       </c>
       <c r="F426" s="10" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="E427" s="10" t="inlineStr">
         <is>
-          <t>모기가 싫어하는 허브오일, / 공기정화, 기분전환</t>
+          <t>모기가 싫어하는 허브오일 · 공기정화, 기분전환</t>
         </is>
       </c>
       <c r="F427" s="10" t="inlineStr">
@@ -16571,12 +16571,12 @@
       </c>
       <c r="E428" s="10" t="inlineStr">
         <is>
-          <t>모기가 싫어하는 허브오일, / 기관지, 비염, 기침관리에 사용하는 허브오일, 기분전환</t>
+          <t>모기가 싫어하는 허브오일 · 기관지, 비염, 기침관리에 사용하는 허브오일, 기분전환</t>
         </is>
       </c>
       <c r="F428" s="10" t="inlineStr">
         <is>
-          <t>제라늄EO, 시나몬EO, / 페파민트EO 등 벌레퇴치효과있는 것</t>
+          <t>제라늄EO, 시나몬EO · 페파민트EO 등 벌레퇴치효과있는 것</t>
         </is>
       </c>
     </row>
@@ -16603,7 +16603,7 @@
       </c>
       <c r="E429" s="10" t="inlineStr">
         <is>
-          <t>귤껍질오일, / 감귤류지만 따뜻한 상큼함, / 공기정화</t>
+          <t>귤껍질오일 · 감귤류지만 따뜻한 상큼함 · 공기정화</t>
         </is>
       </c>
       <c r="F429" s="10" t="inlineStr">
@@ -16933,10 +16933,10 @@
       </c>
       <c r="E444" s="20" t="inlineStr">
         <is>
-          <t>'Rosa'라는 말은 붉은 색을 의미하는 'rodon'이라는 그리스 단어에서 유래했습니다. / 예로부터 이집트에서는 종교와 미용, 향수에 많이 사용했고 로마에서는 목욕과 마사지에 활용해 건강을 유지하는데 사용한 허브입니다. / 로즈는 향수와 오일의 여왕으로 피부와 정신, 신체를 건강하게 합니다. / 로즈의 향기는 가슴 두근거림, 우울증, 불안 초조를 완화 해소시켜주며 여성 호르몬 밸런스 유지에 시너지효과를 발휘합니다.</t>
-        </is>
-      </c>
-      <c r="F444" s="20" t="n"/>
+          <t>'Rosa'라는 말은 붉은 색을 의미하는 'rodon'이라는 그리스 단어에서 유래했습니다. · 예로부터 이집트에서는 종교와 미용, 향수에 많이 사용했고 로마에서는 목욕과 마사지에 활용해 건강을 유지하는데 사용한 허브입니다. · 로즈는 향수와 오일의 여왕으로 피부와 정신, 신체를 건강하게 합니다. · 로즈의 향기는 가슴 두근거림, 우울증, 불안 초조를 완화 해소시켜주며 여성 호르몬 밸런스 유지에 시너지효과를 발휘합니다.</t>
+        </is>
+      </c>
+      <c r="F444" s="20" t="inlineStr"/>
     </row>
     <row r="445" ht="160" customHeight="1">
       <c r="A445" s="20" t="inlineStr">
@@ -16961,10 +16961,10 @@
       </c>
       <c r="E445" s="20" t="inlineStr">
         <is>
-          <t>감미롭고 이국적이며 달콤한 꽃향기로 / 모든 피부에 유효하며 건조해서 손상된 피부나 민감성 피부의 진정, 회복에 효과적이다. / 호르몬균형 , 여성에게는 좋은 오일. 정신피로나 긴장을 완화하는 효과가 높아 스트레스를 해소하고, 자신감을 갖게 한다. 기분을 밝게 하고 고양시키는 효과가 있다.</t>
-        </is>
-      </c>
-      <c r="F445" s="20" t="n"/>
+          <t>감미롭고 이국적이며 달콤한 꽃향기로 · 모든 피부에 유효하며 건조해서 손상된 피부나 민감성 피부의 진정, 회복에 효과적이다. · 호르몬균형 , 여성에게는 좋은 오일. 정신피로나 긴장을 완화하는 효과가 높아 스트레스를 해소하고, 자신감을 갖게 한다. 기분을 밝게 하고 고양시키는 효과가 있다.</t>
+        </is>
+      </c>
+      <c r="F445" s="20" t="inlineStr"/>
     </row>
     <row r="446" ht="14" customHeight="1">
       <c r="A446" s="15" t="inlineStr">
@@ -17136,10 +17136,10 @@
       </c>
       <c r="E455" s="10" t="inlineStr">
         <is>
-          <t>에센셜오일 분산, / 방향용으로 사용시 공기정화, / 소독효과.</t>
-        </is>
-      </c>
-      <c r="F455" s="10" t="n"/>
+          <t>에센셜오일 분산 · 방향용으로 사용시 공기정화 · 소독효과.</t>
+        </is>
+      </c>
+      <c r="F455" s="10" t="inlineStr"/>
     </row>
     <row r="456" ht="48" customHeight="1">
       <c r="A456" s="10" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="E456" s="10" t="inlineStr">
         <is>
-          <t>향이 오랫동안 머물 수 있도록 / 고착제 역할을 함</t>
+          <t>향이 오랫동안 머물 수 있도록 · 고착제 역할을 함</t>
         </is>
       </c>
       <c r="F456" s="10" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="E457" s="10" t="inlineStr">
         <is>
-          <t>허브에서 추출한 100%천연오일. / 모기가 싫어하는 허브에서 추출. / 기존 천연모기퇴치제 레시피 비율에 맞춰 시트로넬라, 레몬글라스, 유칼립투스, 제라늄 EO를 블랜딩한 것. / 모기가 없는 계절에는 방향제, 공기정화제로도 사용가능.</t>
+          <t>허브에서 추출한 100%천연오일. · 모기가 싫어하는 허브에서 추출. · 기존 천연모기퇴치제 레시피 비율에 맞춰 시트로넬라, 레몬글라스, 유칼립투스, 제라늄 EO를 블랜딩한 것. · 모기가 없는 계절에는 방향제, 공기정화제로도 사용가능.</t>
         </is>
       </c>
       <c r="F457" s="10" t="inlineStr">
@@ -17367,7 +17367,7 @@
       </c>
       <c r="F467" s="20" t="inlineStr">
         <is>
-          <t>(식물성)에탄올 / 70% + 식물성 글리세린</t>
+          <t>(식물성)에탄올 · 70% + 식물성 글리세린</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="E468" s="20" t="inlineStr">
         <is>
-          <t>아래표를 참고하세요. / 좋아하거나 가지고 있는 / 오일 한가지 넣어도 됩니다.</t>
+          <t>아래표를 참고하세요. · 좋아하거나 가지고 있는 · 오일 한가지 넣어도 됩니다.</t>
         </is>
       </c>
       <c r="F468" s="20" t="inlineStr">
@@ -17561,7 +17561,7 @@
           <t>탄탄한 유화 안정성, 부드러운 질감, 뛰어난 흡수력</t>
         </is>
       </c>
-      <c r="F477" s="10" t="n"/>
+      <c r="F477" s="10" t="inlineStr"/>
     </row>
     <row r="478" ht="48" customHeight="1">
       <c r="A478" s="10" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F478" s="10" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="F479" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
